--- a/output/finalVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/finalVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1279,9 +1279,9 @@
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】容積率（P002-00 修正百分比）
-填寫值：-6.25
+填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1540,7 +1540,7 @@
     <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(1)土地使用管制 百分比小計（P002-00）
-填寫值：-6.25
+填寫值：6.25
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group1</t>
@@ -1603,9 +1603,9 @@
     <comment ref="G12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
-填寫值：-15.0
+填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1630,9 +1630,9 @@
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
-填寫值：-11.25
+填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1657,9 +1657,9 @@
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
-填寫值：-11.25
+填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1702,9 +1702,9 @@
     <comment ref="G13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1729,9 +1729,9 @@
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1756,9 +1756,9 @@
     <comment ref="M13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1801,9 +1801,9 @@
     <comment ref="G14" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近大型車站之程度（P002-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.near_station</t>
       </text>
     </comment>
@@ -1954,9 +1954,9 @@
     <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】站牌之接近程度或密集程度（P004-00 修正百分比）
-填寫值：-1.0
+填寫值：1.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_busstop</t>
       </text>
     </comment>
@@ -2053,9 +2053,9 @@
     <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】交流道之有無及接近交流道之程度（P004-00 修正百分比）
-填寫值：-1.0
+填寫值：1.0
 資料來源：比準地 P001-00 稍劣(4) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_interchange</t>
       </text>
     </comment>
@@ -2098,9 +2098,9 @@
     <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
-填寫值：-2.5
+填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2125,9 +2125,9 @@
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2152,16 +2152,16 @@
     <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P002-00）
-填寫值：-21.0
+填寫值：21.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2170,7 +2170,7 @@
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P003-00）
-填寫值：-14.75
+填寫值：14.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2179,7 +2179,7 @@
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P004-00）
-填寫值：-16.75
+填寫值：16.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2971,9 +2971,9 @@
     <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P002-00 修正百分比）
-填寫值：4.0
+填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2998,9 +2998,9 @@
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P003-00 修正百分比）
-填寫值：4.0
+填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3025,9 +3025,9 @@
     <comment ref="M28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P004-00 修正百分比）
-填寫值：2.0
+填寫值：-2.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3124,9 +3124,9 @@
     <comment ref="M29" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近公園（里鄰公園、一般公園）、廣場、徒步區之程度（P004-00 修正百分比）
-填寫值：-4.0
+填寫值：4.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 普通(3)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_park</t>
       </text>
     </comment>
@@ -3169,9 +3169,9 @@
     <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P002-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3196,9 +3196,9 @@
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P003-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3223,9 +3223,9 @@
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P004-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3268,9 +3268,9 @@
     <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P002-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3295,9 +3295,9 @@
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P003-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3430,7 +3430,7 @@
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P002-00）
-填寫值：1.0
+填寫值：-1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3439,7 +3439,7 @@
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P003-00）
-填寫值：1.0
+填寫值：-1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3448,7 +3448,7 @@
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P004-00）
-填寫值：-3.5
+填寫值：3.5
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3592,9 +3592,9 @@
     <comment ref="G35" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】殯葬設施之有無及接近程度（P002-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 劣(5) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50
 基準表項目ID：shulin.regional.funeral_facility</t>
       </text>
     </comment>
@@ -3646,9 +3646,9 @@
     <comment ref="M35" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】殯葬設施之有無及接近程度（P004-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 劣(5) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50
 基準表項目ID：shulin.regional.funeral_facility</t>
       </text>
     </comment>
@@ -3754,7 +3754,7 @@
     <comment ref="E37" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(6)特殊設施 百分比小計（P002-00）
-填寫值：2.5
+填寫值：-2.5
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group6</t>
@@ -3772,7 +3772,7 @@
     <comment ref="K37" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(6)特殊設施 百分比小計（P004-00）
-填寫值：2.5
+填寫值：-2.5
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group6</t>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="G8" s="125" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="H8" s="128" t="n">
         <v>3</v>
@@ -5634,7 +5634,7 @@
       <c r="C11" s="65" t="n"/>
       <c r="D11" s="60" t="n"/>
       <c r="E11" s="133" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="F11" s="63" t="n"/>
       <c r="G11" s="134" t="inlineStr">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="G12" s="131" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="H12" s="130" t="n">
         <v>4</v>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="J12" s="131" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="K12" s="130" t="n">
         <v>4</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="M12" s="131" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="N12" s="117" t="n"/>
       <c r="O12" s="111" t="n"/>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="G13" s="131" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="H13" s="130" t="n">
         <v>5</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="J13" s="131" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="K13" s="130" t="n">
         <v>5</v>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="M13" s="131" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="N13" s="117" t="n"/>
       <c r="O13" s="111" t="n"/>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="G14" s="131" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H14" s="130" t="n">
         <v>2</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="M15" s="131" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N15" s="117" t="n"/>
       <c r="O15" s="111" t="n"/>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="M16" s="131" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N16" s="117" t="n"/>
       <c r="O16" s="111" t="n"/>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="G17" s="131" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="H17" s="130" t="n">
         <v>1</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="J17" s="131" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K17" s="130" t="n">
         <v>1</v>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="M17" s="131" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="N17" s="117" t="n"/>
       <c r="O17" s="111" t="n"/>
@@ -5997,7 +5997,7 @@
       <c r="C18" s="65" t="n"/>
       <c r="D18" s="60" t="n"/>
       <c r="E18" s="133" t="n">
-        <v>-21</v>
+        <v>21</v>
       </c>
       <c r="F18" s="63" t="n"/>
       <c r="G18" s="134" t="inlineStr">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="H18" s="133" t="n">
-        <v>-14.75</v>
+        <v>14.75</v>
       </c>
       <c r="I18" s="63" t="n"/>
       <c r="J18" s="134" t="inlineStr">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="K18" s="133" t="n">
-        <v>-16.75</v>
+        <v>16.75</v>
       </c>
       <c r="L18" s="63" t="n"/>
       <c r="M18" s="134" t="inlineStr">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="G28" s="131" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="H28" s="130" t="n">
         <v>1</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="J28" s="131" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="K28" s="130" t="n">
         <v>2</v>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="M28" s="131" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N28" s="117" t="n"/>
       <c r="O28" s="111" t="n"/>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="M29" s="131" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="N29" s="117" t="n"/>
       <c r="O29" s="111" t="n"/>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="G30" s="131" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="H30" s="130" t="n">
         <v>2</v>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="J30" s="131" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="130" t="n">
         <v>2</v>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="M30" s="131" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="N30" s="117" t="n"/>
       <c r="O30" s="111" t="n"/>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G31" s="131" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="H31" s="130" t="n">
         <v>2</v>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="J31" s="131" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="K31" s="130" t="n">
         <v>1</v>
@@ -6768,7 +6768,7 @@
       <c r="C33" s="65" t="n"/>
       <c r="D33" s="60" t="n"/>
       <c r="E33" s="133" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F33" s="63" t="n"/>
       <c r="G33" s="134" t="inlineStr">
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="H33" s="133" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I33" s="63" t="n"/>
       <c r="J33" s="134" t="inlineStr">
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="K33" s="133" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L33" s="63" t="n"/>
       <c r="M33" s="134" t="inlineStr">
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="G35" s="131" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H35" s="130" t="n">
         <v>5</v>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="M35" s="131" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="N35" s="117" t="n"/>
       <c r="O35" s="111" t="n"/>
@@ -6972,7 +6972,7 @@
       <c r="C37" s="65" t="n"/>
       <c r="D37" s="60" t="n"/>
       <c r="E37" s="133" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F37" s="63" t="n"/>
       <c r="G37" s="134" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="K37" s="133" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L37" s="63" t="n"/>
       <c r="M37" s="134" t="inlineStr">
@@ -7217,7 +7217,7 @@
       <c r="C42" s="65" t="n"/>
       <c r="D42" s="60" t="n"/>
       <c r="E42" s="133" t="n">
-        <v>-23.75</v>
+        <v>23.75</v>
       </c>
       <c r="F42" s="63" t="n"/>
       <c r="G42" s="134" t="inlineStr">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="H42" s="133" t="n">
-        <v>-13.75</v>
+        <v>13.75</v>
       </c>
       <c r="I42" s="63" t="n"/>
       <c r="J42" s="134" t="inlineStr">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="K42" s="133" t="n">
-        <v>-17.75</v>
+        <v>17.75</v>
       </c>
       <c r="L42" s="63" t="n"/>
       <c r="M42" s="134" t="inlineStr">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="D62" s="0" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
@@ -10766,7 +10766,7 @@
         </is>
       </c>
       <c r="D95" s="0" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="D98" s="0" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D101" s="0" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
@@ -11214,7 +11214,7 @@
         </is>
       </c>
       <c r="D106" s="0" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
@@ -11336,7 +11336,7 @@
         </is>
       </c>
       <c r="D109" s="0" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
@@ -11458,7 +11458,7 @@
         </is>
       </c>
       <c r="D112" s="0" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="D117" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="D134" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
@@ -12802,7 +12802,7 @@
         </is>
       </c>
       <c r="D145" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="D150" s="0" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="D153" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="D156" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
@@ -16590,7 +16590,7 @@
         </is>
       </c>
       <c r="D238" s="0" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="F238" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G238" s="0" t="inlineStr">
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="D241" s="0" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F241" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G241" s="0" t="inlineStr">
@@ -16834,7 +16834,7 @@
         </is>
       </c>
       <c r="D244" s="0" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="F244" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00</t>
         </is>
       </c>
       <c r="G244" s="0" t="inlineStr">
@@ -17282,7 +17282,7 @@
         </is>
       </c>
       <c r="D255" s="0" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F255" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G255" s="0" t="inlineStr">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="D260" s="0" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="F260" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G260" s="0" t="inlineStr">
@@ -17608,7 +17608,7 @@
         </is>
       </c>
       <c r="D263" s="0" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F263" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G263" s="0" t="inlineStr">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="D266" s="0" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
       </c>
       <c r="F266" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G266" s="0" t="inlineStr">
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="D271" s="0" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
       </c>
       <c r="F271" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G271" s="0" t="inlineStr">
@@ -18056,7 +18056,7 @@
         </is>
       </c>
       <c r="D274" s="0" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="F274" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G274" s="0" t="inlineStr">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="D304" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E304" s="0" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="F304" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G304" s="0" t="inlineStr">
@@ -19522,7 +19522,7 @@
         </is>
       </c>
       <c r="D310" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E310" s="0" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
       </c>
       <c r="F310" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G310" s="0" t="inlineStr">
@@ -20914,7 +20914,7 @@
         </is>
       </c>
       <c r="D344" s="0" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E344" s="0" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         </is>
       </c>
       <c r="D347" s="0" t="n">
-        <v>-21</v>
+        <v>21</v>
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         </is>
       </c>
       <c r="D348" s="0" t="n">
-        <v>-14.75</v>
+        <v>14.75</v>
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="D349" s="0" t="n">
-        <v>-16.75</v>
+        <v>16.75</v>
       </c>
       <c r="E349" s="0" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="D356" s="0" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E356" s="0" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         </is>
       </c>
       <c r="D357" s="0" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E357" s="0" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="D358" s="0" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="E358" s="0" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         </is>
       </c>
       <c r="D359" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E359" s="0" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         </is>
       </c>
       <c r="D361" s="0" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E361" s="0" t="inlineStr">
         <is>

--- a/output/finalVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/finalVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1281,7 +1281,7 @@
         <t>【AI判定】容積率（P002-00 修正百分比）
 填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1605,7 +1605,7 @@
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
 填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1632,7 +1632,7 @@
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1659,7 +1659,7 @@
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1704,7 +1704,7 @@
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1731,7 +1731,7 @@
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1758,7 +1758,7 @@
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1803,7 +1803,7 @@
         <t>【AI判定】接近大型車站之程度（P002-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.near_station</t>
       </text>
     </comment>
@@ -1956,7 +1956,7 @@
         <t>【AI判定】站牌之接近程度或密集程度（P004-00 修正百分比）
 填寫值：1.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_busstop</t>
       </text>
     </comment>
@@ -2055,7 +2055,7 @@
         <t>【AI判定】交流道之有無及接近交流道之程度（P004-00 修正百分比）
 填寫值：1.0
 資料來源：比準地 P001-00 稍劣(4) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_interchange</t>
       </text>
     </comment>
@@ -2100,7 +2100,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
 填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2127,7 +2127,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2154,7 +2154,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2973,7 +2973,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P002-00 修正百分比）
 填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3000,7 +3000,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P003-00 修正百分比）
 填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3027,7 +3027,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P004-00 修正百分比）
 填寫值：-2.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3126,7 +3126,7 @@
         <t>【AI判定】接近公園（里鄰公園、一般公園）、廣場、徒步區之程度（P004-00 修正百分比）
 填寫值：4.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 普通(3)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_park</t>
       </text>
     </comment>
@@ -3171,7 +3171,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P002-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3198,7 +3198,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P003-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3225,7 +3225,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P004-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3270,7 +3270,7 @@
         <t>【AI判定】停車場地之便利程度（P002-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3297,7 +3297,7 @@
         <t>【AI判定】停車場地之便利程度（P003-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3594,7 +3594,7 @@
         <t>【AI判定】殯葬設施之有無及接近程度（P002-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 劣(5) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(4−5)×2.5 = -2.50
 基準表項目ID：shulin.regional.funeral_facility</t>
       </text>
     </comment>
@@ -3648,7 +3648,7 @@
         <t>【AI判定】殯葬設施之有無及接近程度（P004-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 劣(5) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(4−5)×2.5 = -2.50
 基準表項目ID：shulin.regional.funeral_facility</t>
       </text>
     </comment>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="F238" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G238" s="0" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F241" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G241" s="0" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="F244" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00</t>
         </is>
       </c>
       <c r="G244" s="0" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F255" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G255" s="0" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="F260" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G260" s="0" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F263" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G263" s="0" t="inlineStr">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="F266" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G266" s="0" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="F271" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G271" s="0" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="F274" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G274" s="0" t="inlineStr">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="F304" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(4−5)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G304" s="0" t="inlineStr">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="F310" s="0" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(5−4)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(4−5)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G310" s="0" t="inlineStr">
